--- a/Data/Building/Lab.Curtain001.xlsx
+++ b/Data/Building/Lab.Curtain001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252269</v>
+        <v>1711843339</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709269711</v>
+        <v>1711861677</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709270551</v>
+        <v>1711861899</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709263143</v>
+        <v>1711864056</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709263170</v>
+        <v>1711864099</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709263827</v>
+        <v>1711939644</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709263888</v>
+        <v>1711940110</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709350162</v>
+        <v>1712028636</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709350910</v>
+        <v>1712028935</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709351249</v>
+        <v>1712029518</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709351488</v>
+        <v>1712029651</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709435549</v>
+        <v>1712115604</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709435776</v>
+        <v>1712116621</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709437874</v>
+        <v>1712116874</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709438522</v>
+        <v>1712117402</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709520930</v>
+        <v>1712201138</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709520992</v>
+        <v>1712201459</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709524153</v>
+        <v>1712285987</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709524582</v>
+        <v>1712286062</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709611173</v>
+        <v>1712287462</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709611312</v>
+        <v>1712288700</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709611859</v>
+        <v>1712545843</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709611938</v>
+        <v>1712546011</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709865067</v>
+        <v>1712548641</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709865603</v>
+        <v>1712548745</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709866682</v>
+        <v>1712634274</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709867112</v>
+        <v>1712634413</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709952231</v>
+        <v>1712719967</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709952430</v>
+        <v>1712720076</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709953700</v>
+        <v>1712721761</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709954205</v>
+        <v>1712722621</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710040617</v>
+        <v>1712806087</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710040832</v>
+        <v>1712806216</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710043946</v>
+        <v>1712807057</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710044780</v>
+        <v>1712807458</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710129166</v>
+        <v>1712893558</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710129359</v>
+        <v>1712893679</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710129839</v>
+        <v>1713149101</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710130404</v>
+        <v>1713149654</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710215309</v>
+        <v>1713149832</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710215458</v>
+        <v>1713149935</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710215547</v>
+        <v>1713235181</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710216329</v>
+        <v>1713235522</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710472228</v>
+        <v>1713323099</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710472748</v>
+        <v>1713323620</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710472787</v>
+        <v>1713324093</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710472851</v>
+        <v>1713324119</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710559757</v>
+        <v>1713406585</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710560079</v>
+        <v>1713406625</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710647444</v>
+        <v>1713407403</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710647526</v>
+        <v>1713407491</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710647720</v>
+        <v>1713495764</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710647834</v>
+        <v>1713495863</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710731756</v>
+        <v>1713495877</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710732067</v>
+        <v>1713496231</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710732881</v>
+        <v>1713752121</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710733022</v>
+        <v>1713752379</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710818742</v>
+        <v>1713752906</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710818927</v>
+        <v>1713753009</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710819478</v>
+        <v>1713843324</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710819982</v>
+        <v>1713843571</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711077117</v>
+        <v>1713844036</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711077814</v>
+        <v>1713844599</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711078676</v>
+        <v>1713928577</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711079399</v>
+        <v>1713928801</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711164122</v>
+        <v>1713929351</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711164244</v>
+        <v>1713929613</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711164342</v>
+        <v>1714011670</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1711165456</v>
+        <v>1714011829</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1711249231</v>
+        <v>1714011895</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1711249259</v>
+        <v>1714012050</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1711249746</v>
+        <v>1714097671</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1711250388</v>
+        <v>1714097761</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1711336156</v>
+        <v>1714098803</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1711337176</v>
+        <v>1714098966</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,150 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1711423442</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Lab.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1711423991</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Lab.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1711424593</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Lab.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Lab</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1711424861</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Lab.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
